--- a/data/trans_dic/P02E$ssociales-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,45</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,22</t>
+          <t>1,14; 6,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 7,12</t>
+          <t>0,71; 6,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,59</t>
+          <t>1,02; 4,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,73</t>
+          <t>0,52; 4,86</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,35</t>
+          <t>0,56; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,9</t>
+          <t>0,51; 3,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,2</t>
+          <t>0,86; 4,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,43</t>
+          <t>0,67; 2,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,04</t>
+          <t>0,7; 2,79</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,24</t>
+          <t>0,58; 3,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,39</t>
+          <t>0,38; 3,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,83</t>
+          <t>0,63; 2,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,82</t>
+          <t>0,48; 2,91</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,18</t>
+          <t>0,0; 49,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,59</t>
+          <t>0,0; 34,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,19</t>
+          <t>0,36; 3,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,18</t>
+          <t>1,11; 5,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,14</t>
+          <t>0,35; 3,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,54</t>
+          <t>1,38; 5,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,54</t>
+          <t>0,95; 2,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,47</t>
+          <t>0,68; 2,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,06</t>
+          <t>0,19; 1,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,03</t>
+          <t>0,83; 2,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,76</t>
+          <t>0,47; 1,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,86</t>
+          <t>0,17; 0,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,98</t>
+          <t>1,02; 1,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,69</t>
+          <t>0,73; 1,65</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1935</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2023</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4409</t>
+          <t>0; 5263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6851</t>
+          <t>0; 6776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4166</t>
+          <t>0; 5334</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1943</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7070</t>
+          <t>0; 6564</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>0; 5460</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 4621</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7676</t>
+          <t>0; 7898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1994</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2133</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5820</t>
+          <t>0; 5853</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6655</t>
+          <t>0; 7891</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5796</t>
+          <t>0; 5744</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4892</t>
+          <t>0; 4803</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2745; 12091</t>
+          <t>2225; 12470</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>999; 9966</t>
+          <t>999; 9221</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5465</t>
+          <t>0; 5396</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5806</t>
+          <t>0; 4888</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3081; 13937</t>
+          <t>3089; 14503</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1000; 9201</t>
+          <t>1006; 9444</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4711</t>
+          <t>0; 4873</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1928; 11455</t>
+          <t>1908; 11214</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7585</t>
+          <t>0; 7517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2010; 11560</t>
+          <t>2027; 12117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2425; 12978</t>
+          <t>2670; 13990</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4858</t>
+          <t>0; 5499</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5023; 18013</t>
+          <t>4954; 18287</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4131; 17162</t>
+          <t>3985; 15773</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2023</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7008</t>
+          <t>0; 5880</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6517</t>
+          <t>0; 6465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1969; 11603</t>
+          <t>2068; 11304</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>941; 8460</t>
+          <t>938; 8763</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3019; 13970</t>
+          <t>3112; 14223</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1876; 10882</t>
+          <t>1867; 11223</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4678</t>
+          <t>0; 4072</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7078</t>
+          <t>0; 6750</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>890; 7965</t>
+          <t>890; 7771</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3082; 14834</t>
+          <t>3179; 14924</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>898; 8146</t>
+          <t>896; 7818</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4116; 16323</t>
+          <t>4082; 15992</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7214</t>
+          <t>0; 7549</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 6502</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9290; 24976</t>
+          <t>9346; 26343</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5303; 18678</t>
+          <t>5126; 18841</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1789; 10673</t>
+          <t>1870; 10448</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12311; 30680</t>
+          <t>12498; 30365</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5335; 19497</t>
+          <t>5257; 19433</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2843; 14097</t>
+          <t>2745; 13266</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25716; 49589</t>
+          <t>25382; 48721</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12832; 31479</t>
+          <t>13572; 30717</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Clase-trans_dic.xlsx
@@ -688,17 +688,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,41</t>
+          <t>1,46; 6,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,59</t>
+          <t>0,71; 6,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,77</t>
+          <t>1,03; 4,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,86</t>
+          <t>0,51; 4,43</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,28</t>
+          <t>0,55; 3,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,04</t>
+          <t>0,5; 3,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,53</t>
+          <t>0,96; 4,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,47</t>
+          <t>0,68; 2,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,79</t>
+          <t>0,72; 2,8</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,16</t>
+          <t>0,55; 3,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,51</t>
+          <t>0,37; 3,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,19 +1153,19 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,88</t>
+          <t>0,61; 3,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,91</t>
+          <t>0,49; 2,78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1233,22 +1233,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,77</t>
+          <t>0,0; 51,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,9</t>
+          <t>0,0; 34,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,11</t>
+          <t>0,36; 3,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,21</t>
+          <t>1,07; 4,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,01</t>
+          <t>0,35; 3,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,43</t>
+          <t>1,38; 5,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,67</t>
+          <t>1,0; 2,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,49</t>
+          <t>0,71; 2,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,04</t>
+          <t>0,19; 1,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,01</t>
+          <t>0,79; 2,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,75</t>
+          <t>0,48; 1,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,81</t>
+          <t>0,17; 0,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,95</t>
+          <t>1,02; 1,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,65</t>
+          <t>0,69; 1,73</t>
         </is>
       </c>
     </row>
@@ -1649,17 +1649,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5263</t>
+          <t>0; 4439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6776</t>
+          <t>0; 6664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5334</t>
+          <t>0; 5227</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6564</t>
+          <t>0; 6966</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5460</t>
+          <t>0; 4946</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 4402</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7898</t>
+          <t>0; 6771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5853</t>
+          <t>0; 7047</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7891</t>
+          <t>0; 6795</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5744</t>
+          <t>0; 5810</t>
         </is>
       </c>
     </row>
@@ -1965,17 +1965,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4803</t>
+          <t>0; 4586</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2225; 12470</t>
+          <t>2845; 13220</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>999; 9221</t>
+          <t>989; 8861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5396</t>
+          <t>0; 5132</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,17 +1995,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4888</t>
+          <t>0; 4753</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3089; 14503</t>
+          <t>3123; 14359</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1006; 9444</t>
+          <t>997; 8613</t>
         </is>
       </c>
     </row>
@@ -2128,17 +2128,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4873</t>
+          <t>0; 4529</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1908; 11214</t>
+          <t>1881; 10804</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7517</t>
+          <t>0; 6948</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,27 +2148,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2027; 12117</t>
+          <t>2010; 11988</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2670; 13990</t>
+          <t>2959; 13275</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5499</t>
+          <t>0; 4651</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4954; 18287</t>
+          <t>5014; 18118</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3985; 15773</t>
+          <t>4093; 15840</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5880</t>
+          <t>0; 6676</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6465</t>
+          <t>0; 5642</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2068; 11304</t>
+          <t>1975; 11240</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>938; 8763</t>
+          <t>931; 7921</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2326,19 +2326,19 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3112; 14223</t>
+          <t>3030; 15359</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1867; 11223</t>
+          <t>1881; 10709</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4072</t>
+          <t>0; 4181</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6750</t>
+          <t>0; 6610</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>890; 7771</t>
+          <t>890; 7964</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3179; 14924</t>
+          <t>3066; 13638</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,17 +2484,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>896; 7818</t>
+          <t>897; 8941</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4082; 15992</t>
+          <t>4078; 15737</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7549</t>
+          <t>0; 7579</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6502</t>
+          <t>0; 6168</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9346; 26343</t>
+          <t>9871; 25870</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5126; 18841</t>
+          <t>5333; 19082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1870; 10448</t>
+          <t>1909; 11648</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12498; 30365</t>
+          <t>12006; 31295</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5257; 19433</t>
+          <t>5288; 18327</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2745; 13266</t>
+          <t>2827; 12871</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>25382; 48721</t>
+          <t>25566; 48565</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13572; 30717</t>
+          <t>12873; 32311</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
